--- a/Logging_OKANT/Logging_OKANT/Översikt OKÄNT.xlsx
+++ b/Logging_OKANT/Logging_OKANT/Översikt OKÄNT.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z27"/>
+  <dimension ref="A1:Z30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col outlineLevel="1" width="13" customWidth="1" min="22" max="26"/>
@@ -569,7 +569,7 @@
         <v>43419</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -626,7 +626,7 @@
         <v>43690</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -683,7 +683,7 @@
         <v>43735</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -740,7 +740,7 @@
         <v>43780</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>43845</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -854,7 +854,7 @@
         <v>43864</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>43872</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -968,7 +968,7 @@
         <v>43971</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         <v>44005</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>44098</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>44178</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>44224</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>44327</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>44501</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>44707</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
         <v>44729</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         <v>44844</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         <v>45040</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>45086</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
         <v>45092</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -1709,7 +1709,7 @@
         <v>45092</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         <v>45121</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         <v>45124</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -1880,7 +1880,7 @@
         <v>45154</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>45154</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1984,7 +1984,7 @@
       </c>
       <c r="R26" s="2" t="inlineStr"/>
     </row>
-    <row r="27">
+    <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
           <t>A 59354-2023</t>
@@ -1994,7 +1994,7 @@
         <v>45253</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2040,6 +2040,187 @@
         <v>0</v>
       </c>
       <c r="R27" s="2" t="inlineStr"/>
+    </row>
+    <row r="28" ht="15" customHeight="1">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>A 6465-2024</t>
+        </is>
+      </c>
+      <c r="B28" s="1" t="n">
+        <v>45338</v>
+      </c>
+      <c r="C28" s="1" t="n">
+        <v>45340</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>OKÄNT</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>OKÄNT</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29" ht="15" customHeight="1">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>A 6462-2024</t>
+        </is>
+      </c>
+      <c r="B29" s="1" t="n">
+        <v>45338</v>
+      </c>
+      <c r="C29" s="1" t="n">
+        <v>45340</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>OKÄNT</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>OKÄNT</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" s="2" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>A 6508-2024</t>
+        </is>
+      </c>
+      <c r="B30" s="1" t="n">
+        <v>45340</v>
+      </c>
+      <c r="C30" s="1" t="n">
+        <v>45340</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>OKÄNT</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>OKÄNT</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Logging_OKANT/Logging_OKANT/Översikt OKÄNT.xlsx
+++ b/Logging_OKANT/Logging_OKANT/Översikt OKÄNT.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z30"/>
+  <dimension ref="A1:Z27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col outlineLevel="1" width="13" customWidth="1" min="22" max="26"/>
@@ -569,7 +569,7 @@
         <v>43419</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -626,7 +626,7 @@
         <v>43690</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -683,7 +683,7 @@
         <v>43735</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -740,7 +740,7 @@
         <v>43780</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>43845</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -854,7 +854,7 @@
         <v>43864</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>43872</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -968,7 +968,7 @@
         <v>43971</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         <v>44005</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>44098</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>44178</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>44224</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>44327</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>44501</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>44707</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
         <v>44729</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         <v>44844</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         <v>45040</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>45086</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
         <v>45092</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -1709,7 +1709,7 @@
         <v>45092</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         <v>45121</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         <v>45124</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -1880,7 +1880,7 @@
         <v>45154</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>45154</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1984,7 +1984,7 @@
       </c>
       <c r="R26" s="2" t="inlineStr"/>
     </row>
-    <row r="27" ht="15" customHeight="1">
+    <row r="27">
       <c r="A27" t="inlineStr">
         <is>
           <t>A 59354-2023</t>
@@ -1994,7 +1994,7 @@
         <v>45253</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2040,187 +2040,6 @@
         <v>0</v>
       </c>
       <c r="R27" s="2" t="inlineStr"/>
-    </row>
-    <row r="28" ht="15" customHeight="1">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>A 6465-2024</t>
-        </is>
-      </c>
-      <c r="B28" s="1" t="n">
-        <v>45338</v>
-      </c>
-      <c r="C28" s="1" t="n">
-        <v>45340</v>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>OKÄNT</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>OKÄNT</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="G28" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0</v>
-      </c>
-      <c r="I28" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" t="n">
-        <v>0</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R28" s="2" t="inlineStr"/>
-    </row>
-    <row r="29" ht="15" customHeight="1">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>A 6462-2024</t>
-        </is>
-      </c>
-      <c r="B29" s="1" t="n">
-        <v>45338</v>
-      </c>
-      <c r="C29" s="1" t="n">
-        <v>45340</v>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>OKÄNT</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>OKÄNT</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
-      <c r="G29" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
-      <c r="R29" s="2" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>A 6508-2024</t>
-        </is>
-      </c>
-      <c r="B30" s="1" t="n">
-        <v>45340</v>
-      </c>
-      <c r="C30" s="1" t="n">
-        <v>45340</v>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>OKÄNT</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>OKÄNT</t>
-        </is>
-      </c>
-      <c r="G30" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" t="n">
-        <v>0</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R30" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Logging_OKANT/Logging_OKANT/Översikt OKÄNT.xlsx
+++ b/Logging_OKANT/Logging_OKANT/Översikt OKÄNT.xlsx
@@ -569,7 +569,7 @@
         <v>43419</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -626,7 +626,7 @@
         <v>43690</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -683,7 +683,7 @@
         <v>43735</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -740,7 +740,7 @@
         <v>43780</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>43845</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -854,7 +854,7 @@
         <v>43864</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>43872</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -968,7 +968,7 @@
         <v>43971</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         <v>44005</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>44098</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>44178</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>44224</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>44327</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>44501</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>44707</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
         <v>44729</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         <v>44844</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         <v>45040</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>45086</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
         <v>45092</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -1709,7 +1709,7 @@
         <v>45092</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         <v>45121</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         <v>45124</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -1880,7 +1880,7 @@
         <v>45154</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>45154</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1994,7 +1994,7 @@
         <v>45253</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/Logging_OKANT/Logging_OKANT/Översikt OKÄNT.xlsx
+++ b/Logging_OKANT/Logging_OKANT/Översikt OKÄNT.xlsx
@@ -569,7 +569,7 @@
         <v>43419</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -626,7 +626,7 @@
         <v>43690</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -683,7 +683,7 @@
         <v>43735</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -740,7 +740,7 @@
         <v>43780</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>43845</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -854,7 +854,7 @@
         <v>43864</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>43872</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -968,7 +968,7 @@
         <v>43971</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         <v>44005</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>44098</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>44178</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>44224</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>44327</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>44501</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>44707</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
         <v>44729</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         <v>44844</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         <v>45040</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>45086</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
         <v>45092</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -1709,7 +1709,7 @@
         <v>45092</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         <v>45121</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         <v>45124</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -1880,7 +1880,7 @@
         <v>45154</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>45154</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1994,7 +1994,7 @@
         <v>45253</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/Logging_OKANT/Logging_OKANT/Översikt OKÄNT.xlsx
+++ b/Logging_OKANT/Logging_OKANT/Översikt OKÄNT.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z27"/>
+  <dimension ref="A1:Z28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col outlineLevel="1" width="13" customWidth="1" min="22" max="26"/>
@@ -569,7 +569,7 @@
         <v>43419</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -626,7 +626,7 @@
         <v>43690</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -683,7 +683,7 @@
         <v>43735</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -740,7 +740,7 @@
         <v>43780</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>43845</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -854,7 +854,7 @@
         <v>43864</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>43872</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -968,7 +968,7 @@
         <v>43971</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         <v>44005</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>44098</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>44178</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>44224</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>44327</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>44501</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>44707</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
         <v>44729</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         <v>44844</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         <v>45040</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>45086</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
         <v>45092</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -1709,7 +1709,7 @@
         <v>45092</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         <v>45121</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         <v>45124</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -1880,7 +1880,7 @@
         <v>45154</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>45154</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1984,7 +1984,7 @@
       </c>
       <c r="R26" s="2" t="inlineStr"/>
     </row>
-    <row r="27">
+    <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
           <t>A 59354-2023</t>
@@ -1994,7 +1994,7 @@
         <v>45253</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2040,6 +2040,63 @@
         <v>0</v>
       </c>
       <c r="R27" s="2" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>A 7480-2024</t>
+        </is>
+      </c>
+      <c r="B28" s="1" t="n">
+        <v>45346</v>
+      </c>
+      <c r="C28" s="1" t="n">
+        <v>45346</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>OKÄNT</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>OKÄNT</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>1</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Logging_OKANT/Logging_OKANT/Översikt OKÄNT.xlsx
+++ b/Logging_OKANT/Logging_OKANT/Översikt OKÄNT.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z28"/>
+  <dimension ref="A1:Z27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col outlineLevel="1" width="13" customWidth="1" min="22" max="26"/>
@@ -569,7 +569,7 @@
         <v>43419</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -626,7 +626,7 @@
         <v>43690</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -683,7 +683,7 @@
         <v>43735</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -740,7 +740,7 @@
         <v>43780</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>43845</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -854,7 +854,7 @@
         <v>43864</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>43872</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -968,7 +968,7 @@
         <v>43971</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         <v>44005</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>44098</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>44178</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>44224</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>44327</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>44501</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>44707</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
         <v>44729</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         <v>44844</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         <v>45040</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>45086</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
         <v>45092</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -1709,7 +1709,7 @@
         <v>45092</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         <v>45121</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         <v>45124</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -1880,7 +1880,7 @@
         <v>45154</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>45154</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1984,7 +1984,7 @@
       </c>
       <c r="R26" s="2" t="inlineStr"/>
     </row>
-    <row r="27" ht="15" customHeight="1">
+    <row r="27">
       <c r="A27" t="inlineStr">
         <is>
           <t>A 59354-2023</t>
@@ -1994,7 +1994,7 @@
         <v>45253</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2040,63 +2040,6 @@
         <v>0</v>
       </c>
       <c r="R27" s="2" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>A 7480-2024</t>
-        </is>
-      </c>
-      <c r="B28" s="1" t="n">
-        <v>45346</v>
-      </c>
-      <c r="C28" s="1" t="n">
-        <v>45346</v>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>OKÄNT</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>OKÄNT</t>
-        </is>
-      </c>
-      <c r="G28" t="n">
-        <v>1</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0</v>
-      </c>
-      <c r="I28" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" t="n">
-        <v>0</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R28" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Logging_OKANT/Logging_OKANT/Översikt OKÄNT.xlsx
+++ b/Logging_OKANT/Logging_OKANT/Översikt OKÄNT.xlsx
@@ -569,7 +569,7 @@
         <v>43419</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -626,7 +626,7 @@
         <v>43690</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -683,7 +683,7 @@
         <v>43735</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -740,7 +740,7 @@
         <v>43780</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>43845</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -854,7 +854,7 @@
         <v>43864</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>43872</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -968,7 +968,7 @@
         <v>43971</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         <v>44005</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>44098</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>44178</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>44224</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>44327</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>44501</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>44707</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
         <v>44729</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         <v>44844</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         <v>45040</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>45086</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
         <v>45092</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -1709,7 +1709,7 @@
         <v>45092</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         <v>45121</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         <v>45124</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -1880,7 +1880,7 @@
         <v>45154</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>45154</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1994,7 +1994,7 @@
         <v>45253</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/Logging_OKANT/Logging_OKANT/Översikt OKÄNT.xlsx
+++ b/Logging_OKANT/Logging_OKANT/Översikt OKÄNT.xlsx
@@ -569,7 +569,7 @@
         <v>43419</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -626,7 +626,7 @@
         <v>43690</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -683,7 +683,7 @@
         <v>43735</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -740,7 +740,7 @@
         <v>43780</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>43845</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -854,7 +854,7 @@
         <v>43864</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>43872</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -968,7 +968,7 @@
         <v>43971</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         <v>44005</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>44098</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>44178</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>44224</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>44327</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>44501</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>44707</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
         <v>44729</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         <v>44844</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         <v>45040</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>45086</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
         <v>45092</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -1709,7 +1709,7 @@
         <v>45092</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         <v>45121</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         <v>45124</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -1880,7 +1880,7 @@
         <v>45154</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>45154</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1994,7 +1994,7 @@
         <v>45253</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/Logging_OKANT/Logging_OKANT/Översikt OKÄNT.xlsx
+++ b/Logging_OKANT/Logging_OKANT/Översikt OKÄNT.xlsx
@@ -569,7 +569,7 @@
         <v>43419</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -626,7 +626,7 @@
         <v>43690</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -683,7 +683,7 @@
         <v>43735</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -740,7 +740,7 @@
         <v>43780</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>43845</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -854,7 +854,7 @@
         <v>43864</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>43872</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -968,7 +968,7 @@
         <v>43971</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         <v>44005</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>44098</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>44178</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>44224</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>44327</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>44501</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>44707</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
         <v>44729</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         <v>44844</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         <v>45040</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>45086</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
         <v>45092</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -1709,7 +1709,7 @@
         <v>45092</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         <v>45121</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         <v>45124</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -1880,7 +1880,7 @@
         <v>45154</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>45154</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1994,7 +1994,7 @@
         <v>45253</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/Logging_OKANT/Logging_OKANT/Översikt OKÄNT.xlsx
+++ b/Logging_OKANT/Logging_OKANT/Översikt OKÄNT.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z27"/>
+  <dimension ref="A1:Z31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col outlineLevel="1" width="13" customWidth="1" min="22" max="26"/>
@@ -562,14 +562,14 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A 59460-2018</t>
+          <t>A 7984-2024</t>
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>43419</v>
+        <v>45348</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -582,16 +582,16 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -606,27 +606,55 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R2" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="R2" s="2" t="inlineStr">
+        <is>
+          <t>Strandlummer</t>
+        </is>
+      </c>
+      <c r="S2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_SVERIGE/Logging_0000/Logging_0000/artfynd/A 7984-2024 artfynd.xlsx", "A 7984-2024")</f>
+        <v/>
+      </c>
+      <c r="T2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_SVERIGE/Logging_0000/Logging_0000/kartor/A 7984-2024 karta.png", "A 7984-2024")</f>
+        <v/>
+      </c>
+      <c r="V2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_SVERIGE/Logging_0000/Logging_0000/klagomål/A 7984-2024 FSC-klagomål.docx", "A 7984-2024")</f>
+        <v/>
+      </c>
+      <c r="W2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_SVERIGE/Logging_0000/Logging_0000/klagomålsmail/A 7984-2024 FSC-klagomål mail.docx", "A 7984-2024")</f>
+        <v/>
+      </c>
+      <c r="X2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_SVERIGE/Logging_0000/Logging_0000/tillsyn/A 7984-2024 tillsynsbegäran.docx", "A 7984-2024")</f>
+        <v/>
+      </c>
+      <c r="Y2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_SVERIGE/Logging_0000/Logging_0000/tillsynsmail/A 7984-2024 tillsynsbegäran mail.docx", "A 7984-2024")</f>
+        <v/>
+      </c>
     </row>
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 39332-2019</t>
+          <t>A 59460-2018</t>
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>43690</v>
+        <v>43419</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -639,7 +667,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>7.8</v>
+        <v>0.8</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -676,14 +704,14 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 53209-2019</t>
+          <t>A 39332-2019</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
-        <v>43735</v>
+        <v>43690</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -696,7 +724,7 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.6</v>
+        <v>7.8</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -733,14 +761,14 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 60954-2019</t>
+          <t>A 53209-2019</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
-        <v>43780</v>
+        <v>43735</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -753,7 +781,7 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -790,14 +818,14 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 3368-2020</t>
+          <t>A 60954-2019</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
-        <v>43845</v>
+        <v>43780</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -810,7 +838,7 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -847,14 +875,14 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 6001-2020</t>
+          <t>A 3368-2020</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
-        <v>43864</v>
+        <v>43845</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -867,7 +895,7 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -904,14 +932,14 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 7659-2020</t>
+          <t>A 6001-2020</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
-        <v>43872</v>
+        <v>43864</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -924,7 +952,7 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>5</v>
+        <v>1.7</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -961,14 +989,14 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 24198-2020</t>
+          <t>A 7659-2020</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
-        <v>43971</v>
+        <v>43872</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -981,7 +1009,7 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0.5</v>
+        <v>5</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -1018,14 +1046,14 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 28558-2020</t>
+          <t>A 24198-2020</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
-        <v>44005</v>
+        <v>43971</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1038,7 +1066,7 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>3.6</v>
+        <v>0.5</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -1075,14 +1103,14 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 48612-2020</t>
+          <t>A 28558-2020</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
-        <v>44098</v>
+        <v>44005</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1095,7 +1123,7 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0.9</v>
+        <v>3.6</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -1132,14 +1160,14 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 67002-2020</t>
+          <t>A 48612-2020</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
-        <v>44178</v>
+        <v>44098</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1189,14 +1217,14 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 5090-2021</t>
+          <t>A 67002-2020</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
-        <v>44224</v>
+        <v>44178</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1209,7 +1237,7 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>4.9</v>
+        <v>0.9</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -1246,14 +1274,14 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 22663-2021</t>
+          <t>A 5090-2021</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
-        <v>44327</v>
+        <v>44224</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1266,7 +1294,7 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>1.5</v>
+        <v>4.9</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -1303,14 +1331,14 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 61532-2021</t>
+          <t>A 22663-2021</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
-        <v>44501</v>
+        <v>44327</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1323,7 +1351,7 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -1360,14 +1388,14 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 21686-2022</t>
+          <t>A 61532-2021</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
-        <v>44707</v>
+        <v>44501</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1380,7 +1408,7 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>2.2</v>
+        <v>0.6</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1417,14 +1445,14 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 25221-2022</t>
+          <t>A 21686-2022</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
-        <v>44729</v>
+        <v>44707</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1437,7 +1465,7 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>5.4</v>
+        <v>2.2</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -1474,14 +1502,14 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 45797-2022</t>
+          <t>A 25221-2022</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
-        <v>44844</v>
+        <v>44729</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1494,7 +1522,7 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>2.5</v>
+        <v>5.4</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -1531,14 +1559,14 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 17976-2023</t>
+          <t>A 45797-2022</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>45040</v>
+        <v>44844</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1551,7 +1579,7 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>9.6</v>
+        <v>2.5</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -1588,14 +1616,14 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 26234-2023</t>
+          <t>A 17976-2023</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
-        <v>45086</v>
+        <v>45040</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1608,7 +1636,7 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>2.3</v>
+        <v>9.6</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -1645,14 +1673,14 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 26451-2023</t>
+          <t>A 26234-2023</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
-        <v>45092</v>
+        <v>45086</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -1665,7 +1693,7 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -1702,14 +1730,14 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 27505-2023</t>
+          <t>A 26451-2023</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
         <v>45092</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -1722,7 +1750,7 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -1759,14 +1787,14 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 33852-2023</t>
+          <t>A 27505-2023</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
-        <v>45121</v>
+        <v>45092</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -1779,7 +1807,7 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>8.5</v>
+        <v>2.5</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -1816,14 +1844,14 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 34013-2023</t>
+          <t>A 33852-2023</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
-        <v>45124</v>
+        <v>45121</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -1836,7 +1864,7 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>1.4</v>
+        <v>8.5</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -1873,14 +1901,14 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 36814-2023</t>
+          <t>A 34013-2023</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
-        <v>45154</v>
+        <v>45124</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1893,7 +1921,7 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>4.4</v>
+        <v>1.4</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -1930,14 +1958,14 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 36808-2023</t>
+          <t>A 36814-2023</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
         <v>45154</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1950,96 +1978,324 @@
         </is>
       </c>
       <c r="G26" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" s="2" t="inlineStr"/>
+    </row>
+    <row r="27" ht="15" customHeight="1">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>A 36808-2023</t>
+        </is>
+      </c>
+      <c r="B27" s="1" t="n">
+        <v>45154</v>
+      </c>
+      <c r="C27" s="1" t="n">
+        <v>45351</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>OKÄNT</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>OKÄNT</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
         <v>2.1</v>
       </c>
-      <c r="H26" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
-      <c r="R26" s="2" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" s="2" t="inlineStr"/>
+    </row>
+    <row r="28" ht="15" customHeight="1">
+      <c r="A28" t="inlineStr">
         <is>
           <t>A 59354-2023</t>
         </is>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B28" s="1" t="n">
         <v>45253</v>
       </c>
-      <c r="C27" s="1" t="n">
-        <v>45350</v>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>OKÄNT</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>OKÄNT</t>
-        </is>
-      </c>
-      <c r="G27" t="n">
+      <c r="C28" s="1" t="n">
+        <v>45351</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>OKÄNT</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>OKÄNT</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
         <v>2.2</v>
       </c>
-      <c r="H27" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
-      <c r="R27" s="2" t="inlineStr"/>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29" ht="15" customHeight="1">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>A 7981-2024</t>
+        </is>
+      </c>
+      <c r="B29" s="1" t="n">
+        <v>45348</v>
+      </c>
+      <c r="C29" s="1" t="n">
+        <v>45351</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>OKÄNT</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>OKÄNT</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" s="2" t="inlineStr"/>
+    </row>
+    <row r="30" ht="15" customHeight="1">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>A 7971-2024</t>
+        </is>
+      </c>
+      <c r="B30" s="1" t="n">
+        <v>45348</v>
+      </c>
+      <c r="C30" s="1" t="n">
+        <v>45351</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>OKÄNT</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>OKÄNT</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" s="2" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>A 7979-2024</t>
+        </is>
+      </c>
+      <c r="B31" s="1" t="n">
+        <v>45348</v>
+      </c>
+      <c r="C31" s="1" t="n">
+        <v>45351</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>OKÄNT</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>OKÄNT</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Logging_OKANT/Logging_OKANT/Översikt OKÄNT.xlsx
+++ b/Logging_OKANT/Logging_OKANT/Översikt OKÄNT.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z31"/>
+  <dimension ref="A1:Z28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col outlineLevel="1" width="13" customWidth="1" min="22" max="26"/>
@@ -562,14 +562,14 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A 7984-2024</t>
+          <t>A 59460-2018</t>
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>45348</v>
+        <v>43419</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -582,16 +582,16 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -606,55 +606,27 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>1</v>
-      </c>
-      <c r="R2" s="2" t="inlineStr">
-        <is>
-          <t>Strandlummer</t>
-        </is>
-      </c>
-      <c r="S2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_SVERIGE/Logging_0000/Logging_0000/artfynd/A 7984-2024 artfynd.xlsx", "A 7984-2024")</f>
-        <v/>
-      </c>
-      <c r="T2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_SVERIGE/Logging_0000/Logging_0000/kartor/A 7984-2024 karta.png", "A 7984-2024")</f>
-        <v/>
-      </c>
-      <c r="V2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_SVERIGE/Logging_0000/Logging_0000/klagomål/A 7984-2024 FSC-klagomål.docx", "A 7984-2024")</f>
-        <v/>
-      </c>
-      <c r="W2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_SVERIGE/Logging_0000/Logging_0000/klagomålsmail/A 7984-2024 FSC-klagomål mail.docx", "A 7984-2024")</f>
-        <v/>
-      </c>
-      <c r="X2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_SVERIGE/Logging_0000/Logging_0000/tillsyn/A 7984-2024 tillsynsbegäran.docx", "A 7984-2024")</f>
-        <v/>
-      </c>
-      <c r="Y2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_SVERIGE/Logging_0000/Logging_0000/tillsynsmail/A 7984-2024 tillsynsbegäran mail.docx", "A 7984-2024")</f>
-        <v/>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="R2" s="2" t="inlineStr"/>
     </row>
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 59460-2018</t>
+          <t>A 39332-2019</t>
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>43419</v>
+        <v>43690</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -667,7 +639,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.8</v>
+        <v>7.8</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -704,14 +676,14 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 39332-2019</t>
+          <t>A 53209-2019</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
-        <v>43690</v>
+        <v>43735</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -724,7 +696,7 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>7.8</v>
+        <v>0.6</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -761,14 +733,14 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 53209-2019</t>
+          <t>A 60954-2019</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
-        <v>43735</v>
+        <v>43780</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -781,7 +753,7 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -818,14 +790,14 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 60954-2019</t>
+          <t>A 3368-2020</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
-        <v>43780</v>
+        <v>43845</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -838,7 +810,7 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -875,14 +847,14 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 3368-2020</t>
+          <t>A 6001-2020</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
-        <v>43845</v>
+        <v>43864</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -895,7 +867,7 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -932,14 +904,14 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 6001-2020</t>
+          <t>A 7659-2020</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
-        <v>43864</v>
+        <v>43872</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -952,7 +924,7 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>1.7</v>
+        <v>5</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -989,14 +961,14 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 7659-2020</t>
+          <t>A 24198-2020</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
-        <v>43872</v>
+        <v>43971</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1009,7 +981,7 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -1046,14 +1018,14 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 24198-2020</t>
+          <t>A 28558-2020</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
-        <v>43971</v>
+        <v>44005</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1066,7 +1038,7 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0.5</v>
+        <v>3.6</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -1103,14 +1075,14 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 28558-2020</t>
+          <t>A 48612-2020</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
-        <v>44005</v>
+        <v>44098</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1123,7 +1095,7 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>3.6</v>
+        <v>0.9</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -1160,14 +1132,14 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 48612-2020</t>
+          <t>A 67002-2020</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
-        <v>44098</v>
+        <v>44178</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1217,14 +1189,14 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 67002-2020</t>
+          <t>A 5090-2021</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
-        <v>44178</v>
+        <v>44224</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1237,7 +1209,7 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0.9</v>
+        <v>4.9</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -1274,14 +1246,14 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 5090-2021</t>
+          <t>A 22663-2021</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
-        <v>44224</v>
+        <v>44327</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1294,7 +1266,7 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>4.9</v>
+        <v>1.5</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -1331,14 +1303,14 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 22663-2021</t>
+          <t>A 61532-2021</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
-        <v>44327</v>
+        <v>44501</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1351,7 +1323,7 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -1388,14 +1360,14 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 61532-2021</t>
+          <t>A 21686-2022</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
-        <v>44501</v>
+        <v>44707</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1408,7 +1380,7 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>0.6</v>
+        <v>2.2</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1445,14 +1417,14 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 21686-2022</t>
+          <t>A 25221-2022</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
-        <v>44707</v>
+        <v>44729</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1465,7 +1437,7 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>2.2</v>
+        <v>5.4</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -1502,14 +1474,14 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 25221-2022</t>
+          <t>A 45797-2022</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
-        <v>44729</v>
+        <v>44844</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1522,7 +1494,7 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>5.4</v>
+        <v>2.5</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -1559,14 +1531,14 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 45797-2022</t>
+          <t>A 17976-2023</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>44844</v>
+        <v>45040</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1579,7 +1551,7 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>2.5</v>
+        <v>9.6</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -1616,14 +1588,14 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 17976-2023</t>
+          <t>A 26234-2023</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
-        <v>45040</v>
+        <v>45086</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1636,7 +1608,7 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>9.6</v>
+        <v>2.3</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -1673,14 +1645,14 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 26234-2023</t>
+          <t>A 26451-2023</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
-        <v>45086</v>
+        <v>45092</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -1693,7 +1665,7 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -1730,14 +1702,14 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 26451-2023</t>
+          <t>A 27505-2023</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
         <v>45092</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -1750,7 +1722,7 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -1787,14 +1759,14 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 27505-2023</t>
+          <t>A 33852-2023</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
-        <v>45092</v>
+        <v>45121</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -1807,7 +1779,7 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>2.5</v>
+        <v>8.5</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -1844,14 +1816,14 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 33852-2023</t>
+          <t>A 34013-2023</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
-        <v>45121</v>
+        <v>45124</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -1864,7 +1836,7 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>8.5</v>
+        <v>1.4</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -1901,14 +1873,14 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 34013-2023</t>
+          <t>A 36814-2023</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
-        <v>45124</v>
+        <v>45154</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1921,7 +1893,7 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>1.4</v>
+        <v>4.4</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -1958,14 +1930,14 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 36814-2023</t>
+          <t>A 36808-2023</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
         <v>45154</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1978,7 +1950,7 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>4.4</v>
+        <v>2.1</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -2015,71 +1987,71 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 36808-2023</t>
+          <t>A 59354-2023</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>45154</v>
+        <v>45253</v>
       </c>
       <c r="C27" s="1" t="n">
+        <v>45352</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>OKÄNT</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>OKÄNT</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" s="2" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>A 8188-2024</t>
+        </is>
+      </c>
+      <c r="B28" s="1" t="n">
         <v>45351</v>
       </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>OKÄNT</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>OKÄNT</t>
-        </is>
-      </c>
-      <c r="G27" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="H27" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
-      <c r="R27" s="2" t="inlineStr"/>
-    </row>
-    <row r="28" ht="15" customHeight="1">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>A 59354-2023</t>
-        </is>
-      </c>
-      <c r="B28" s="1" t="n">
-        <v>45253</v>
-      </c>
       <c r="C28" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2091,8 +2063,13 @@
           <t>OKÄNT</t>
         </is>
       </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="G28" t="n">
-        <v>2.2</v>
+        <v>4.3</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -2125,177 +2102,6 @@
         <v>0</v>
       </c>
       <c r="R28" s="2" t="inlineStr"/>
-    </row>
-    <row r="29" ht="15" customHeight="1">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>A 7981-2024</t>
-        </is>
-      </c>
-      <c r="B29" s="1" t="n">
-        <v>45348</v>
-      </c>
-      <c r="C29" s="1" t="n">
-        <v>45351</v>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>OKÄNT</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>OKÄNT</t>
-        </is>
-      </c>
-      <c r="G29" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
-      <c r="R29" s="2" t="inlineStr"/>
-    </row>
-    <row r="30" ht="15" customHeight="1">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>A 7971-2024</t>
-        </is>
-      </c>
-      <c r="B30" s="1" t="n">
-        <v>45348</v>
-      </c>
-      <c r="C30" s="1" t="n">
-        <v>45351</v>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>OKÄNT</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>OKÄNT</t>
-        </is>
-      </c>
-      <c r="G30" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" t="n">
-        <v>0</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R30" s="2" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>A 7979-2024</t>
-        </is>
-      </c>
-      <c r="B31" s="1" t="n">
-        <v>45348</v>
-      </c>
-      <c r="C31" s="1" t="n">
-        <v>45351</v>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>OKÄNT</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>OKÄNT</t>
-        </is>
-      </c>
-      <c r="G31" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="H31" t="n">
-        <v>0</v>
-      </c>
-      <c r="I31" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
-      <c r="R31" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Logging_OKANT/Logging_OKANT/Översikt OKÄNT.xlsx
+++ b/Logging_OKANT/Logging_OKANT/Översikt OKÄNT.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z28"/>
+  <dimension ref="A1:Z27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col outlineLevel="1" width="13" customWidth="1" min="22" max="26"/>
@@ -569,7 +569,7 @@
         <v>43419</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -626,7 +626,7 @@
         <v>43690</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -683,7 +683,7 @@
         <v>43735</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -740,7 +740,7 @@
         <v>43780</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>43845</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -854,7 +854,7 @@
         <v>43864</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>43872</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -968,7 +968,7 @@
         <v>43971</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         <v>44005</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>44098</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>44178</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>44224</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>44327</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>44501</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>44707</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
         <v>44729</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         <v>44844</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         <v>45040</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>45086</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
         <v>45092</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -1709,7 +1709,7 @@
         <v>45092</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         <v>45121</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         <v>45124</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -1880,7 +1880,7 @@
         <v>45154</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>45154</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1984,7 +1984,7 @@
       </c>
       <c r="R26" s="2" t="inlineStr"/>
     </row>
-    <row r="27" ht="15" customHeight="1">
+    <row r="27">
       <c r="A27" t="inlineStr">
         <is>
           <t>A 59354-2023</t>
@@ -1994,7 +1994,7 @@
         <v>45253</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2040,68 +2040,6 @@
         <v>0</v>
       </c>
       <c r="R27" s="2" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>A 8188-2024</t>
-        </is>
-      </c>
-      <c r="B28" s="1" t="n">
-        <v>45351</v>
-      </c>
-      <c r="C28" s="1" t="n">
-        <v>45352</v>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>OKÄNT</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>OKÄNT</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
-      <c r="G28" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0</v>
-      </c>
-      <c r="I28" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" t="n">
-        <v>0</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R28" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Logging_OKANT/Logging_OKANT/Översikt OKÄNT.xlsx
+++ b/Logging_OKANT/Logging_OKANT/Översikt OKÄNT.xlsx
@@ -569,7 +569,7 @@
         <v>43419</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -626,7 +626,7 @@
         <v>43690</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -683,7 +683,7 @@
         <v>43735</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -740,7 +740,7 @@
         <v>43780</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>43845</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -854,7 +854,7 @@
         <v>43864</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>43872</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -968,7 +968,7 @@
         <v>43971</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         <v>44005</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>44098</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>44178</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>44224</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>44327</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>44501</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>44707</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
         <v>44729</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         <v>44844</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         <v>45040</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>45086</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
         <v>45092</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -1709,7 +1709,7 @@
         <v>45092</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         <v>45121</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         <v>45124</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -1880,7 +1880,7 @@
         <v>45154</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>45154</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1994,7 +1994,7 @@
         <v>45253</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/Logging_OKANT/Logging_OKANT/Översikt OKÄNT.xlsx
+++ b/Logging_OKANT/Logging_OKANT/Översikt OKÄNT.xlsx
@@ -569,7 +569,7 @@
         <v>43419</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -626,7 +626,7 @@
         <v>43690</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -683,7 +683,7 @@
         <v>43735</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -740,7 +740,7 @@
         <v>43780</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>43845</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -854,7 +854,7 @@
         <v>43864</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>43872</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -968,7 +968,7 @@
         <v>43971</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         <v>44005</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>44098</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>44178</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>44224</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>44327</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>44501</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>44707</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
         <v>44729</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         <v>44844</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         <v>45040</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>45086</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
         <v>45092</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -1709,7 +1709,7 @@
         <v>45092</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         <v>45121</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         <v>45124</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -1880,7 +1880,7 @@
         <v>45154</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>45154</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1994,7 +1994,7 @@
         <v>45253</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/Logging_OKANT/Logging_OKANT/Översikt OKÄNT.xlsx
+++ b/Logging_OKANT/Logging_OKANT/Översikt OKÄNT.xlsx
@@ -569,7 +569,7 @@
         <v>43419</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -626,7 +626,7 @@
         <v>43690</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -683,7 +683,7 @@
         <v>43735</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -740,7 +740,7 @@
         <v>43780</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>43845</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -854,7 +854,7 @@
         <v>43864</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>43872</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -968,7 +968,7 @@
         <v>43971</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         <v>44005</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>44098</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>44178</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>44224</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>44327</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>44501</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>44707</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
         <v>44729</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         <v>44844</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         <v>45040</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>45086</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
         <v>45092</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -1709,7 +1709,7 @@
         <v>45092</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         <v>45121</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         <v>45124</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -1880,7 +1880,7 @@
         <v>45154</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>45154</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1994,7 +1994,7 @@
         <v>45253</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/Logging_OKANT/Logging_OKANT/Översikt OKÄNT.xlsx
+++ b/Logging_OKANT/Logging_OKANT/Översikt OKÄNT.xlsx
@@ -569,7 +569,7 @@
         <v>43419</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -626,7 +626,7 @@
         <v>43690</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -683,7 +683,7 @@
         <v>43735</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -740,7 +740,7 @@
         <v>43780</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>43845</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -854,7 +854,7 @@
         <v>43864</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>43872</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -968,7 +968,7 @@
         <v>43971</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         <v>44005</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>44098</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>44178</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>44224</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>44327</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>44501</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>44707</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
         <v>44729</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         <v>44844</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         <v>45040</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>45086</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
         <v>45092</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -1709,7 +1709,7 @@
         <v>45092</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         <v>45121</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         <v>45124</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -1880,7 +1880,7 @@
         <v>45154</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>45154</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1994,7 +1994,7 @@
         <v>45253</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/Logging_OKANT/Logging_OKANT/Översikt OKÄNT.xlsx
+++ b/Logging_OKANT/Logging_OKANT/Översikt OKÄNT.xlsx
@@ -569,7 +569,7 @@
         <v>43419</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -626,7 +626,7 @@
         <v>43690</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -683,7 +683,7 @@
         <v>43735</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -740,7 +740,7 @@
         <v>43780</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>43845</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -854,7 +854,7 @@
         <v>43864</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>43872</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -968,7 +968,7 @@
         <v>43971</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         <v>44005</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>44098</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>44178</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>44224</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>44327</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>44501</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>44707</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
         <v>44729</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         <v>44844</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         <v>45040</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>45086</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
         <v>45092</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -1709,7 +1709,7 @@
         <v>45092</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         <v>45121</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         <v>45124</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -1880,7 +1880,7 @@
         <v>45154</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>45154</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1994,7 +1994,7 @@
         <v>45253</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/Logging_OKANT/Logging_OKANT/Översikt OKÄNT.xlsx
+++ b/Logging_OKANT/Logging_OKANT/Översikt OKÄNT.xlsx
@@ -569,7 +569,7 @@
         <v>43419</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45358</v>
+        <v>45359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -626,7 +626,7 @@
         <v>43690</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45358</v>
+        <v>45359</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -683,7 +683,7 @@
         <v>43735</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45358</v>
+        <v>45359</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -740,7 +740,7 @@
         <v>43780</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45358</v>
+        <v>45359</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>43845</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45358</v>
+        <v>45359</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -854,7 +854,7 @@
         <v>43864</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45358</v>
+        <v>45359</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>43872</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45358</v>
+        <v>45359</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -968,7 +968,7 @@
         <v>43971</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45358</v>
+        <v>45359</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         <v>44005</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45358</v>
+        <v>45359</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>44098</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45358</v>
+        <v>45359</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>44178</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45358</v>
+        <v>45359</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>44224</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45358</v>
+        <v>45359</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>44327</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45358</v>
+        <v>45359</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>44501</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45358</v>
+        <v>45359</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>44707</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45358</v>
+        <v>45359</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
         <v>44729</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45358</v>
+        <v>45359</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         <v>44844</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45358</v>
+        <v>45359</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         <v>45040</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45358</v>
+        <v>45359</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>45086</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45358</v>
+        <v>45359</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
         <v>45092</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45358</v>
+        <v>45359</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -1709,7 +1709,7 @@
         <v>45092</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45358</v>
+        <v>45359</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         <v>45121</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45358</v>
+        <v>45359</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         <v>45124</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45358</v>
+        <v>45359</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -1880,7 +1880,7 @@
         <v>45154</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45358</v>
+        <v>45359</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>45154</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45358</v>
+        <v>45359</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1994,7 +1994,7 @@
         <v>45253</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45358</v>
+        <v>45359</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/Logging_OKANT/Logging_OKANT/Översikt OKÄNT.xlsx
+++ b/Logging_OKANT/Logging_OKANT/Översikt OKÄNT.xlsx
@@ -569,7 +569,7 @@
         <v>43419</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45359</v>
+        <v>45360</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -626,7 +626,7 @@
         <v>43690</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45359</v>
+        <v>45360</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -683,7 +683,7 @@
         <v>43735</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45359</v>
+        <v>45360</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -740,7 +740,7 @@
         <v>43780</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45359</v>
+        <v>45360</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>43845</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45359</v>
+        <v>45360</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -854,7 +854,7 @@
         <v>43864</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45359</v>
+        <v>45360</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>43872</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45359</v>
+        <v>45360</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -968,7 +968,7 @@
         <v>43971</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45359</v>
+        <v>45360</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         <v>44005</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45359</v>
+        <v>45360</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>44098</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45359</v>
+        <v>45360</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>44178</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45359</v>
+        <v>45360</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>44224</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45359</v>
+        <v>45360</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>44327</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45359</v>
+        <v>45360</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>44501</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45359</v>
+        <v>45360</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>44707</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45359</v>
+        <v>45360</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
         <v>44729</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45359</v>
+        <v>45360</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         <v>44844</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45359</v>
+        <v>45360</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         <v>45040</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45359</v>
+        <v>45360</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>45086</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45359</v>
+        <v>45360</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
         <v>45092</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45359</v>
+        <v>45360</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -1709,7 +1709,7 @@
         <v>45092</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45359</v>
+        <v>45360</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         <v>45121</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45359</v>
+        <v>45360</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         <v>45124</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45359</v>
+        <v>45360</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -1880,7 +1880,7 @@
         <v>45154</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45359</v>
+        <v>45360</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>45154</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45359</v>
+        <v>45360</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1994,7 +1994,7 @@
         <v>45253</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45359</v>
+        <v>45360</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/Logging_OKANT/Logging_OKANT/Översikt OKÄNT.xlsx
+++ b/Logging_OKANT/Logging_OKANT/Översikt OKÄNT.xlsx
@@ -569,7 +569,7 @@
         <v>43419</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45360</v>
+        <v>45361</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -626,7 +626,7 @@
         <v>43690</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45360</v>
+        <v>45361</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -683,7 +683,7 @@
         <v>43735</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45360</v>
+        <v>45361</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -740,7 +740,7 @@
         <v>43780</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45360</v>
+        <v>45361</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>43845</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45360</v>
+        <v>45361</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -854,7 +854,7 @@
         <v>43864</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45360</v>
+        <v>45361</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>43872</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45360</v>
+        <v>45361</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -968,7 +968,7 @@
         <v>43971</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45360</v>
+        <v>45361</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         <v>44005</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45360</v>
+        <v>45361</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>44098</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45360</v>
+        <v>45361</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>44178</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45360</v>
+        <v>45361</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>44224</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45360</v>
+        <v>45361</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>44327</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45360</v>
+        <v>45361</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>44501</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45360</v>
+        <v>45361</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>44707</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45360</v>
+        <v>45361</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
         <v>44729</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45360</v>
+        <v>45361</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         <v>44844</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45360</v>
+        <v>45361</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         <v>45040</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45360</v>
+        <v>45361</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>45086</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45360</v>
+        <v>45361</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
         <v>45092</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45360</v>
+        <v>45361</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -1709,7 +1709,7 @@
         <v>45092</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45360</v>
+        <v>45361</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         <v>45121</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45360</v>
+        <v>45361</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         <v>45124</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45360</v>
+        <v>45361</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -1880,7 +1880,7 @@
         <v>45154</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45360</v>
+        <v>45361</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>45154</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45360</v>
+        <v>45361</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1994,7 +1994,7 @@
         <v>45253</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45360</v>
+        <v>45361</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/Logging_OKANT/Logging_OKANT/Översikt OKÄNT.xlsx
+++ b/Logging_OKANT/Logging_OKANT/Översikt OKÄNT.xlsx
@@ -569,7 +569,7 @@
         <v>43419</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45361</v>
+        <v>45362</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -626,7 +626,7 @@
         <v>43690</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45361</v>
+        <v>45362</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -683,7 +683,7 @@
         <v>43735</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45361</v>
+        <v>45362</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -740,7 +740,7 @@
         <v>43780</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45361</v>
+        <v>45362</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>43845</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45361</v>
+        <v>45362</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -854,7 +854,7 @@
         <v>43864</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45361</v>
+        <v>45362</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>43872</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45361</v>
+        <v>45362</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -968,7 +968,7 @@
         <v>43971</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45361</v>
+        <v>45362</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         <v>44005</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45361</v>
+        <v>45362</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>44098</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45361</v>
+        <v>45362</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>44178</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45361</v>
+        <v>45362</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>44224</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45361</v>
+        <v>45362</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>44327</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45361</v>
+        <v>45362</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>44501</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45361</v>
+        <v>45362</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>44707</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45361</v>
+        <v>45362</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
         <v>44729</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45361</v>
+        <v>45362</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         <v>44844</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45361</v>
+        <v>45362</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         <v>45040</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45361</v>
+        <v>45362</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>45086</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45361</v>
+        <v>45362</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
         <v>45092</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45361</v>
+        <v>45362</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -1709,7 +1709,7 @@
         <v>45092</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45361</v>
+        <v>45362</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         <v>45121</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45361</v>
+        <v>45362</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         <v>45124</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45361</v>
+        <v>45362</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -1880,7 +1880,7 @@
         <v>45154</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45361</v>
+        <v>45362</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>45154</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45361</v>
+        <v>45362</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1994,7 +1994,7 @@
         <v>45253</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45361</v>
+        <v>45362</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/Logging_OKANT/Logging_OKANT/Översikt OKÄNT.xlsx
+++ b/Logging_OKANT/Logging_OKANT/Översikt OKÄNT.xlsx
@@ -569,7 +569,7 @@
         <v>43419</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45362</v>
+        <v>45363</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -626,7 +626,7 @@
         <v>43690</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45362</v>
+        <v>45363</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -683,7 +683,7 @@
         <v>43735</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45362</v>
+        <v>45363</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -740,7 +740,7 @@
         <v>43780</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45362</v>
+        <v>45363</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>43845</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45362</v>
+        <v>45363</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -854,7 +854,7 @@
         <v>43864</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45362</v>
+        <v>45363</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>43872</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45362</v>
+        <v>45363</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -968,7 +968,7 @@
         <v>43971</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45362</v>
+        <v>45363</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         <v>44005</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45362</v>
+        <v>45363</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>44098</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45362</v>
+        <v>45363</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>44178</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45362</v>
+        <v>45363</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>44224</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45362</v>
+        <v>45363</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>44327</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45362</v>
+        <v>45363</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>44501</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45362</v>
+        <v>45363</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>44707</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45362</v>
+        <v>45363</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
         <v>44729</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45362</v>
+        <v>45363</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         <v>44844</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45362</v>
+        <v>45363</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         <v>45040</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45362</v>
+        <v>45363</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>45086</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45362</v>
+        <v>45363</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
         <v>45092</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45362</v>
+        <v>45363</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -1709,7 +1709,7 @@
         <v>45092</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45362</v>
+        <v>45363</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         <v>45121</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45362</v>
+        <v>45363</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         <v>45124</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45362</v>
+        <v>45363</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -1880,7 +1880,7 @@
         <v>45154</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45362</v>
+        <v>45363</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>45154</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45362</v>
+        <v>45363</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1994,7 +1994,7 @@
         <v>45253</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45362</v>
+        <v>45363</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/Logging_OKANT/Logging_OKANT/Översikt OKÄNT.xlsx
+++ b/Logging_OKANT/Logging_OKANT/Översikt OKÄNT.xlsx
@@ -569,7 +569,7 @@
         <v>43419</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45363</v>
+        <v>45364</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -626,7 +626,7 @@
         <v>43690</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45363</v>
+        <v>45364</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -683,7 +683,7 @@
         <v>43735</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45363</v>
+        <v>45364</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -740,7 +740,7 @@
         <v>43780</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45363</v>
+        <v>45364</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>43845</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45363</v>
+        <v>45364</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -854,7 +854,7 @@
         <v>43864</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45363</v>
+        <v>45364</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>43872</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45363</v>
+        <v>45364</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -968,7 +968,7 @@
         <v>43971</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45363</v>
+        <v>45364</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         <v>44005</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45363</v>
+        <v>45364</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>44098</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45363</v>
+        <v>45364</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>44178</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45363</v>
+        <v>45364</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>44224</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45363</v>
+        <v>45364</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>44327</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45363</v>
+        <v>45364</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>44501</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45363</v>
+        <v>45364</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>44707</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45363</v>
+        <v>45364</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
         <v>44729</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45363</v>
+        <v>45364</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         <v>44844</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45363</v>
+        <v>45364</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         <v>45040</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45363</v>
+        <v>45364</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>45086</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45363</v>
+        <v>45364</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
         <v>45092</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45363</v>
+        <v>45364</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -1709,7 +1709,7 @@
         <v>45092</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45363</v>
+        <v>45364</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         <v>45121</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45363</v>
+        <v>45364</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         <v>45124</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45363</v>
+        <v>45364</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -1880,7 +1880,7 @@
         <v>45154</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45363</v>
+        <v>45364</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>45154</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45363</v>
+        <v>45364</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1994,7 +1994,7 @@
         <v>45253</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45363</v>
+        <v>45364</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
